--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 13,66</t>
+          <t>0,52; 13,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 8,34</t>
+          <t>-5,06; 8,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,82; -5,43</t>
+          <t>-17,38; -5,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 10,97</t>
+          <t>-5,77; 10,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 10,01</t>
+          <t>-5,47; 9,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -7,91</t>
+          <t>-21,14; -7,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 10,41</t>
+          <t>0,17; 10,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 7,3</t>
+          <t>-2,8; 7,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -8,45</t>
+          <t>-16,81; -7,55</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 34,74</t>
+          <t>1,39; 35,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 20,75</t>
+          <t>-10,8; 21,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -13,12</t>
+          <t>-37,72; -13,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 24,85</t>
+          <t>-10,59; 23,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 22,29</t>
+          <t>-10,38; 22,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,52; -17,84</t>
+          <t>-40,5; -18,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 24,27</t>
+          <t>0,35; 24,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 16,9</t>
+          <t>-5,92; 17,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -19,44</t>
+          <t>-35,64; -17,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 14,83</t>
+          <t>0,24; 15,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 10,46</t>
+          <t>-4,29; 10,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,97; -4,98</t>
+          <t>-18,76; -5,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 16,06</t>
+          <t>0,58; 15,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 4,66</t>
+          <t>-10,59; 4,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,87; -15,74</t>
+          <t>-29,17; -15,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 13,11</t>
+          <t>2,87; 13,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,76</t>
+          <t>-5,2; 6,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,79; -12,6</t>
+          <t>-21,79; -12,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 36,75</t>
+          <t>0,73; 37,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 26,51</t>
+          <t>-9,42; 25,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -12,32</t>
+          <t>-39,76; -13,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 32,65</t>
+          <t>0,67; 31,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 9,36</t>
+          <t>-19,03; 8,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,04; -32,44</t>
+          <t>-51,87; -32,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 28,58</t>
+          <t>5,67; 29,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 10,39</t>
+          <t>-10,21; 13,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,58; -27,23</t>
+          <t>-42,92; -26,67</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 18,36</t>
+          <t>6,34; 17,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 16,65</t>
+          <t>4,12; 15,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,2; -11,74</t>
+          <t>-38,41; -11,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 23,46</t>
+          <t>4,14; 23,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 20,25</t>
+          <t>0,15; 21,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,67; -1,09</t>
+          <t>-21,32; -2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,95; 18,17</t>
+          <t>8,63; 18,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 16,0</t>
+          <t>4,95; 15,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-39,53; -10,77</t>
+          <t>-37,84; -11,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,92; 44,43</t>
+          <t>13,04; 43,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,57; 39,24</t>
+          <t>8,73; 38,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,17; -26,54</t>
+          <t>-81,62; -25,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 47,08</t>
+          <t>6,64; 46,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 40,93</t>
+          <t>0,11; 41,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,59; -2,05</t>
+          <t>-35,07; -4,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,83; 40,78</t>
+          <t>17,3; 40,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 36,09</t>
+          <t>9,87; 34,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-78,85; -22,76</t>
+          <t>-75,33; -23,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 12,51</t>
+          <t>4,57; 12,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 8,36</t>
+          <t>0,33; 8,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -7,1</t>
+          <t>-15,64; -7,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,29</t>
+          <t>-1,97; 8,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -0,85</t>
+          <t>-10,66; -0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 15,49</t>
+          <t>-23,8; 13,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,97</t>
+          <t>3,74; 10,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,67</t>
+          <t>-2,66; 3,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 6,47</t>
+          <t>-16,34; 9,91</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 26,53</t>
+          <t>8,89; 26,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,97; 18,06</t>
+          <t>0,72; 18,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,46; -15,04</t>
+          <t>-31,05; -15,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 16,14</t>
+          <t>-3,25; 14,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -1,5</t>
+          <t>-17,17; -1,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 26,62</t>
+          <t>-39,55; 24,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 19,52</t>
+          <t>6,81; 19,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 7,21</t>
+          <t>-4,92; 7,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 12,49</t>
+          <t>-30,91; 20,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 14,79</t>
+          <t>0,93; 15,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 11,6</t>
+          <t>-2,57; 10,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -3,71</t>
+          <t>-17,4; -3,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,25; 18,04</t>
+          <t>7,27; 18,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 14,39</t>
+          <t>3,98; 14,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,11; -11,24</t>
+          <t>-29,7; -10,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,15; 14,64</t>
+          <t>6,2; 15,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,21</t>
+          <t>1,71; 10,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -9,88</t>
+          <t>-22,72; -9,8</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2,61; 33,65</t>
+          <t>1,34; 36,13</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 25,23</t>
+          <t>-4,98; 25,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,16; -8,05</t>
+          <t>-33,58; -6,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,42; 31,58</t>
+          <t>11,35; 31,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,66; 25,18</t>
+          <t>6,2; 25,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,12; -19,0</t>
+          <t>-46,81; -18,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,41; 27,09</t>
+          <t>10,55; 28,73</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,82; 19,27</t>
+          <t>2,94; 19,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,33; -18,43</t>
+          <t>-40,15; -18,39</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,9; 20,95</t>
+          <t>5,97; 21,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,86; 15,48</t>
+          <t>1,14; 15,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 12,47</t>
+          <t>-8,52; 13,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,19</t>
+          <t>2,42; 10,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,81</t>
+          <t>-2,74; 5,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,14; -17,63</t>
+          <t>-26,23; -17,62</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76; 11,21</t>
+          <t>3,45; 11,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 5,58</t>
+          <t>-1,88; 5,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -13,91</t>
+          <t>-22,69; -14,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21,99; 107,87</t>
+          <t>21,22; 105,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5,9; 76,79</t>
+          <t>3,67; 77,32</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 58,46</t>
+          <t>-33,9; 63,71</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,49; 15,79</t>
+          <t>3,53; 16,08</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 7,44</t>
+          <t>-4,04; 7,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -26,87</t>
+          <t>-38,54; -27,09</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,27; 19,66</t>
+          <t>5,75; 19,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 9,86</t>
+          <t>-3,05; 9,48</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -24,73</t>
+          <t>-38,19; -24,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,98</t>
+          <t>7,0; 11,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,05</t>
+          <t>2,76; 7,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,46; -9,29</t>
+          <t>-19,66; -9,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,9; 9,5</t>
+          <t>4,67; 9,51</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,23</t>
+          <t>-1,7; 3,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-22,14; -6,22</t>
+          <t>-21,86; -6,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,95</t>
+          <t>6,69; 10,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,72</t>
+          <t>1,38; 4,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -9,53</t>
+          <t>-18,86; -9,2</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,59; 27,74</t>
+          <t>15,35; 27,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6,83; 18,7</t>
+          <t>6,06; 18,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -21,41</t>
+          <t>-43,03; -21,23</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,04</t>
+          <t>7,57; 16,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,39</t>
+          <t>-2,79; 5,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -10,19</t>
+          <t>-35,92; -11,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,37</t>
+          <t>12,49; 19,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,08</t>
+          <t>2,67; 9,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,3; -18,53</t>
+          <t>-35,75; -17,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-11,26</t>
+          <t>-11,4</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,76</t>
+          <t>-14,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-12,47</t>
+          <t>-12,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 13,83</t>
+          <t>0,59; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 8,59</t>
+          <t>-4,46; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,38; -5,32</t>
+          <t>-17,12; -4,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 10,37</t>
+          <t>-6,81; 9,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 9,9</t>
+          <t>-6,3; 8,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -7,87</t>
+          <t>-21,67; -7,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 10,58</t>
+          <t>0,4; 10,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 7,3</t>
+          <t>-3,01; 7,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,81; -7,55</t>
+          <t>-17,4; -7,98</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-26,22%</t>
+          <t>-26,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,35%</t>
+          <t>-30,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-27,6%</t>
+          <t>-27,68%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 35,06</t>
+          <t>1,3; 35,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 21,7</t>
+          <t>-9,83; 22,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -13,06</t>
+          <t>-37,64; -12,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 23,3</t>
+          <t>-13,13; 22,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 22,35</t>
+          <t>-12,25; 20,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,5; -18,27</t>
+          <t>-40,69; -17,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 24,98</t>
+          <t>0,91; 25,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 17,16</t>
+          <t>-6,21; 17,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,64; -17,54</t>
+          <t>-35,87; -18,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,72</t>
+          <t>-12,6</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-22,33</t>
+          <t>-22,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,96</t>
+          <t>-17,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 15,03</t>
+          <t>0,2; 15,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 10,34</t>
+          <t>-3,8; 10,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; -5,15</t>
+          <t>-19,43; -5,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 15,69</t>
+          <t>1,14; 16,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 4,17</t>
+          <t>-10,82; 4,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,17; -15,76</t>
+          <t>-28,7; -16,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 13,38</t>
+          <t>2,16; 13,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 6,03</t>
+          <t>-5,09; 5,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-21,79; -12,2</t>
+          <t>-22,74; -12,9</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,59%</t>
+          <t>-28,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,6%</t>
+          <t>-43,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-35,13%</t>
+          <t>-36,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 37,33</t>
+          <t>0,56; 37,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 25,18</t>
+          <t>-8,12; 27,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,76; -13,28</t>
+          <t>-40,79; -13,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 31,42</t>
+          <t>2,07; 33,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 8,3</t>
+          <t>-18,85; 9,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,87; -32,9</t>
+          <t>-51,64; -33,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 29,7</t>
+          <t>4,08; 28,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 13,1</t>
+          <t>-10,05; 12,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,92; -26,67</t>
+          <t>-43,92; -28,5</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-24,87</t>
+          <t>-14,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,64</t>
+          <t>-12,02</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-22,62</t>
+          <t>-13,24</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 17,98</t>
+          <t>6,12; 17,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 15,74</t>
+          <t>4,28; 16,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,41; -11,18</t>
+          <t>-20,69; -8,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 23,31</t>
+          <t>4,31; 23,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 21,13</t>
+          <t>-0,41; 20,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -2,28</t>
+          <t>-21,67; -2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 18,03</t>
+          <t>8,5; 18,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 15,6</t>
+          <t>5,21; 16,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-37,84; -11,06</t>
+          <t>-18,17; -8,18</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-55,11%</t>
+          <t>-32,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-20,79%</t>
+          <t>-21,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-47,43%</t>
+          <t>-27,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 43,15</t>
+          <t>12,79; 42,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,73; 38,0</t>
+          <t>8,8; 39,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,62; -25,5</t>
+          <t>-43,52; -20,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 46,86</t>
+          <t>7,38; 46,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 41,65</t>
+          <t>-0,51; 40,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,07; -4,56</t>
+          <t>-35,29; -4,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,3; 40,79</t>
+          <t>17,21; 40,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,87; 34,79</t>
+          <t>10,35; 36,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-75,33; -23,58</t>
+          <t>-36,61; -18,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,5</t>
+          <t>-12,75</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,19</t>
+          <t>-23,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,06</t>
+          <t>-16,47</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,58</t>
+          <t>4,48; 12,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 8,67</t>
+          <t>0,32; 8,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -7,13</t>
+          <t>-16,63; -8,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 8,42</t>
+          <t>-1,77; 8,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,66; -0,61</t>
+          <t>-11,3; -1,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 13,83</t>
+          <t>-27,72; -18,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,74; 10,03</t>
+          <t>3,76; 9,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 3,84</t>
+          <t>-2,28; 3,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 9,91</t>
+          <t>-19,39; -13,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-23,7%</t>
+          <t>-26,28%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,44%</t>
+          <t>-38,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,25%</t>
+          <t>-31,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 26,8</t>
+          <t>8,77; 27,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 18,66</t>
+          <t>0,9; 18,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -15,54</t>
+          <t>-33,26; -18,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 14,82</t>
+          <t>-2,86; 15,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -1,09</t>
+          <t>-18,14; -2,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 24,63</t>
+          <t>-44,88; -32,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,81; 19,66</t>
+          <t>6,94; 19,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 7,56</t>
+          <t>-4,11; 7,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,91; 20,09</t>
+          <t>-36,09; -26,38</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-10,31</t>
+          <t>-13,96</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-17,92</t>
+          <t>-14,0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,92</t>
+          <t>-14,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 15,69</t>
+          <t>0,68; 14,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 10,97</t>
+          <t>-2,18; 11,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,4; -3,04</t>
+          <t>-20,96; -7,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,27; 18,13</t>
+          <t>7,21; 18,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,77</t>
+          <t>3,87; 14,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-29,7; -10,88</t>
+          <t>-19,26; -9,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,2; 15,25</t>
+          <t>6,6; 15,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,27</t>
+          <t>1,91; 10,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-22,72; -9,8</t>
+          <t>-18,13; -9,99</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-21,26%</t>
+          <t>-28,78%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,45%</t>
+          <t>-23,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-26,58%</t>
+          <t>-25,46%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,34; 36,13</t>
+          <t>1,41; 32,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 25,22</t>
+          <t>-4,27; 25,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,58; -6,79</t>
+          <t>-39,84; -16,32</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,35; 31,53</t>
+          <t>11,27; 31,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,2; 25,9</t>
+          <t>5,96; 25,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,81; -18,18</t>
+          <t>-30,03; -15,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,55; 28,73</t>
+          <t>11,18; 29,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,94; 19,14</t>
+          <t>3,29; 20,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -18,39</t>
+          <t>-31,28; -18,99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>-1,61</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-21,86</t>
+          <t>-22,59</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-18,27</t>
+          <t>-19,13</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,97; 21,36</t>
+          <t>5,31; 21,05</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,14; 15,42</t>
+          <t>0,69; 14,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 13,85</t>
+          <t>-10,56; 8,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,42; 10,31</t>
+          <t>1,79; 9,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,13</t>
+          <t>-2,78; 4,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,23; -17,62</t>
+          <t>-26,83; -18,54</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,45; 11,15</t>
+          <t>3,98; 10,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,36</t>
+          <t>-1,48; 5,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-22,69; -14,25</t>
+          <t>-23,19; -15,24</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>-6,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-32,81%</t>
+          <t>-33,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-31,33%</t>
+          <t>-32,8%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>21,22; 105,12</t>
+          <t>19,39; 103,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,67; 77,32</t>
+          <t>2,14; 72,74</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 63,71</t>
+          <t>-41,86; 40,49</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,53; 16,08</t>
+          <t>2,55; 14,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 7,95</t>
+          <t>-4,1; 7,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-38,54; -27,09</t>
+          <t>-39,43; -28,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,75; 19,72</t>
+          <t>6,66; 18,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 9,48</t>
+          <t>-2,5; 10,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-38,19; -24,68</t>
+          <t>-38,89; -26,78</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,78</t>
+          <t>-11,74</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-17,52</t>
+          <t>-20,58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-15,12</t>
+          <t>-16,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,0; 11,99</t>
+          <t>7,15; 11,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,76</t>
+          <t>2,94; 7,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -9,36</t>
+          <t>-14,28; -9,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,51</t>
+          <t>4,97; 9,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,15</t>
+          <t>-1,6; 3,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -6,84</t>
+          <t>-22,76; -18,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,07</t>
+          <t>6,6; 9,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,83</t>
+          <t>1,27; 4,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -9,2</t>
+          <t>-17,83; -14,54</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-28,79%</t>
+          <t>-26,45%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-29,0%</t>
+          <t>-34,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-28,78%</t>
+          <t>-30,82%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>15,35; 27,88</t>
+          <t>15,95; 27,81</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,28</t>
+          <t>6,44; 17,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,03; -21,23</t>
+          <t>-31,59; -21,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,57; 16,15</t>
+          <t>8,1; 16,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 5,32</t>
+          <t>-2,61; 5,36</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-35,92; -11,33</t>
+          <t>-36,75; -30,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,49; 19,57</t>
+          <t>12,34; 19,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,51</t>
+          <t>2,39; 9,4</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,75; -17,37</t>
+          <t>-33,5; -28,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
